--- a/skincare-products-data-dict.xlsx
+++ b/skincare-products-data-dict.xlsx
@@ -290,7 +290,7 @@
     <t>pdf</t>
   </si>
   <si>
-    <t>dermatologic_diseases</t>
+    <t>dermatologic_diseases, ingredient_treatments</t>
   </si>
   <si>
     <t>name</t>
